--- a/diseases/d053/2020-2025.xlsx
+++ b/diseases/d053/2020-2025.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1658,6 +1663,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2395,6 +2405,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3132,6 +3147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4017,6 +4037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4754,6 +4779,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5491,6 +5521,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6376,6 +6411,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7113,6 +7153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7850,6 +7895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8735,6 +8785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9472,6 +9527,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10357,6 +10417,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11094,6 +11159,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11831,6 +11901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12568,6 +12643,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13453,6 +13533,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14190,6 +14275,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14927,6 +15017,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15812,6 +15907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16549,6 +16649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17434,6 +17539,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18171,6 +18281,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18908,6 +19023,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19793,6 +19913,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20530,6 +20655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21267,6 +21397,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22152,6 +22287,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22889,6 +23029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23626,6 +23771,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24511,6 +24661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25248,6 +25403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25985,6 +26145,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26870,6 +27035,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27607,6 +27777,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28344,6 +28519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29229,6 +29409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29966,6 +30151,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30703,6 +30893,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31736,6 +31931,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32473,6 +32673,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33210,6 +33415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34095,6 +34305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34832,6 +35047,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35717,6 +35937,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36454,6 +36679,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37191,6 +37421,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38076,6 +38311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38813,6 +39053,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39550,6 +39795,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40435,6 +40685,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41172,6 +41427,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41909,6 +42169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42794,6 +43059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43531,6 +43801,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO292" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44268,6 +44543,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45153,6 +45433,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45890,6 +46175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46775,6 +47065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO314" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -47512,6 +47807,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO319" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -48249,6 +48549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO324" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49134,6 +49439,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49871,6 +50181,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO335" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50608,6 +50923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO340" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51345,6 +51665,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO345" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52230,6 +52555,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO351" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52967,6 +53297,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA356" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO356" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53852,6 +54187,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA362" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO362" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -54589,6 +54929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA367" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO367" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -55326,6 +55671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA372" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO372" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56211,6 +56561,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA378" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO378" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -56946,6 +57301,11 @@
       <c r="S383" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA383" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO383" t="inlineStr">
